--- a/files/ALIEXPRESS_ALLROAD/Fasteners.xlsx
+++ b/files/ALIEXPRESS_ALLROAD/Fasteners.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Documents\anthony-r-h.github.io\files\ALIEXPRESS_ALLROAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98745A67-1832-4EFF-B4D2-6C27D6F6B995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA20EDED-36A7-45A6-A718-30DAE8B57B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29340" yWindow="8505" windowWidth="27615" windowHeight="20655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29055" yWindow="4800" windowWidth="27615" windowHeight="20655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/files/ALIEXPRESS_ALLROAD/Fasteners.xlsx
+++ b/files/ALIEXPRESS_ALLROAD/Fasteners.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Documents\anthony-r-h.github.io\files\ALIEXPRESS_ALLROAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA20EDED-36A7-45A6-A718-30DAE8B57B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E055C7E-EA67-44B6-BC3B-3FF01C28E888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29055" yWindow="4800" windowWidth="27615" windowHeight="20655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29835" yWindow="3990" windowWidth="27615" windowHeight="20655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="77">
   <si>
     <t>Fastener</t>
   </si>
@@ -74,9 +74,6 @@
     <t>No grip paste</t>
   </si>
   <si>
-    <t>T30 Torx</t>
-  </si>
-  <si>
     <t>M6x30mm titanium</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>Caliper to flat mount adapter</t>
   </si>
   <si>
-    <t>Flat mount adapter to frame/fork</t>
-  </si>
-  <si>
     <t>5-8 Nm</t>
   </si>
   <si>
@@ -116,21 +110,9 @@
     <t>10 Nm</t>
   </si>
   <si>
-    <t>Front derailler (high, low, adjustment)</t>
-  </si>
-  <si>
-    <t>Rear derailler (high, low, adjustment)</t>
-  </si>
-  <si>
-    <t>Rear derailleur mount</t>
-  </si>
-  <si>
     <t>Front derailleur mount</t>
   </si>
   <si>
-    <t>Front derailleur braze on attachment</t>
-  </si>
-  <si>
     <t>Water bottle mount</t>
   </si>
   <si>
@@ -140,21 +122,12 @@
     <t>T25 torx</t>
   </si>
   <si>
-    <t>Low torque</t>
-  </si>
-  <si>
     <t>Rear thru-axle</t>
   </si>
   <si>
     <t>Front thru-axle</t>
   </si>
   <si>
-    <t xml:space="preserve">M12x168mm (P1.5, 16L) 7075 aluminum </t>
-  </si>
-  <si>
-    <t xml:space="preserve">M12x121mm (P1.5, 17L) 7075 aluminum </t>
-  </si>
-  <si>
     <t>6mm hex</t>
   </si>
   <si>
@@ -170,36 +143,21 @@
     <t>3mm hex</t>
   </si>
   <si>
-    <t>Casette</t>
-  </si>
-  <si>
     <t>Lockring</t>
   </si>
   <si>
-    <t>Casette tool</t>
-  </si>
-  <si>
     <t>40 Nm</t>
   </si>
   <si>
-    <t>Rotor disk</t>
-  </si>
-  <si>
     <t xml:space="preserve">Headset top cap </t>
   </si>
   <si>
-    <t>Compression plug</t>
-  </si>
-  <si>
     <t>Expander screw</t>
   </si>
   <si>
     <t>Just enough to remove play</t>
   </si>
   <si>
-    <t>By feel</t>
-  </si>
-  <si>
     <t>Rear derailleur cable pinch screw</t>
   </si>
   <si>
@@ -225,10 +183,6 @@
   </si>
   <si>
     <t>Self-extracting crank bolt</t>
-  </si>
-  <si>
-    <t>Casette tool
-20-tooth bottom bracket tool</t>
   </si>
   <si>
     <t>16-notch bottom bracket tool</t>
@@ -257,6 +211,64 @@
   </si>
   <si>
     <t>35-40 Nm</t>
+  </si>
+  <si>
+    <t>M5x12mm 304 screw</t>
+  </si>
+  <si>
+    <t>Flat mount adapter to frame (rear)</t>
+  </si>
+  <si>
+    <t>Flat mount adapter to frame (fork)</t>
+  </si>
+  <si>
+    <t>M5x12mm titanium screw with washer</t>
+  </si>
+  <si>
+    <t>M5x10mm titanium screw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rear derailleur </t>
+  </si>
+  <si>
+    <t>Mount bolt</t>
+  </si>
+  <si>
+    <t>T30 torx</t>
+  </si>
+  <si>
+    <t>Front derailleur (high, low, adjustment)</t>
+  </si>
+  <si>
+    <t>Rear derailleur (high, low, adjustment)</t>
+  </si>
+  <si>
+    <t>Cassette</t>
+  </si>
+  <si>
+    <t>Cassette tool</t>
+  </si>
+  <si>
+    <t>Cassette tool
+20-tooth bottom bracket tool</t>
+  </si>
+  <si>
+    <t>Brake rotor</t>
+  </si>
+  <si>
+    <t>M5x35mm titanium screw with washer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M12x168mm (P1.5, 16L) 7075 aluminium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M12x121mm (P1.5, 17L) 7075 aluminium </t>
+  </si>
+  <si>
+    <t>Loctite 242 (minimal)</t>
+  </si>
+  <si>
+    <t>Fork compression plug</t>
   </si>
 </sst>
 </file>
@@ -277,18 +289,12 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -308,10 +314,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,7 +625,7 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -641,10 +647,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -658,327 +664,370 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
+        <v>60</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>53</v>
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
